--- a/VerveStacks_CHE_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHE_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{535A8968-E010-40C5-80AC-BFF74EACEE21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{159DA1A1-D216-4CA5-9690-C356EE0A701E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2953,7 +2953,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60D3A904-88D8-48FE-ABBC-5DAD9EC918FC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83BEFEC0-FE90-40D7-A732-1756F36CAF40}">
   <dimension ref="B2:AI381"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_CHE_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHE_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{159DA1A1-D216-4CA5-9690-C356EE0A701E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5117F95C-6788-44EE-B5BD-2BDB01AEB8E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2953,7 +2953,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83BEFEC0-FE90-40D7-A732-1756F36CAF40}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FB7D7CE-730A-420C-AA22-30C5E2A97E73}">
   <dimension ref="B2:AI381"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_CHE_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHE_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5117F95C-6788-44EE-B5BD-2BDB01AEB8E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{54C9B655-0F51-4EBD-983F-38D057F65C52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2953,7 +2953,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FB7D7CE-730A-420C-AA22-30C5E2A97E73}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9EDE50E-0371-466C-A7E1-FA0DFEB08D77}">
   <dimension ref="B2:AI381"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_CHE_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHE_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{54C9B655-0F51-4EBD-983F-38D057F65C52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{45AAAFF1-476B-4970-B389-2E8064B59A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2953,7 +2953,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9EDE50E-0371-466C-A7E1-FA0DFEB08D77}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE435208-E1E6-45EF-8EC3-C262DEC95BCD}">
   <dimension ref="B2:AI381"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_CHE_grids/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_CHE_grids/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{45AAAFF1-476B-4970-B389-2E8064B59A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{02C2C14B-DEBA-4052-8D29-0E5C0ADBA7EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2953,7 +2953,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE435208-E1E6-45EF-8EC3-C262DEC95BCD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B898B1E9-E628-4918-99FE-E0CE08C734B0}">
   <dimension ref="B2:AI381"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
